--- a/emotion_grading.xlsx
+++ b/emotion_grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\HCIproj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF0E8AE-BECC-46BB-BFFA-33175A94611B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63660DF-CC7A-4552-9C48-A65B0C121CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3048" yWindow="3276" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4632" yWindow="3120" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="117">
   <si>
     <t>emoji</t>
   </si>
@@ -272,32 +272,141 @@
     <t>\U0001F632</t>
   </si>
   <si>
+    <t>\U0001F62D</t>
+  </si>
+  <si>
+    <t>😡</t>
+  </si>
+  <si>
+    <t>\U0001F621</t>
+  </si>
+  <si>
+    <t>🤬</t>
+  </si>
+  <si>
+    <t>🤡</t>
+  </si>
+  <si>
+    <t>\U0001F921</t>
+  </si>
+  <si>
+    <t>0-0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.95-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🥹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.99-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3-0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>😣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\U0001F623</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>😭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\U0001F92C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5-0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>\U0001F979</t>
-  </si>
-  <si>
-    <t>\U0001F62D</t>
-  </si>
-  <si>
-    <t>😡</t>
-  </si>
-  <si>
-    <t>\U0001F621</t>
-  </si>
-  <si>
-    <t>🤬</t>
-  </si>
-  <si>
-    <t>🤡</t>
-  </si>
-  <si>
-    <t>\U0001F921</t>
-  </si>
-  <si>
-    <t>0-0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.95-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9999-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5-0.96</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -305,75 +414,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0-0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0-0.01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>🥹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.99-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2-0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0-0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3-0.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>😣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\U0001F623</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>😭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\U0001F92C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0-0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.89-0.99</t>
+    <t>0.2-0.7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -714,6 +755,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -805,19 +847,19 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -992,14 +1034,14 @@
       <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="F11" t="s">
-        <v>12</v>
+      <c r="F11" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1019,13 +1061,13 @@
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1045,13 +1087,13 @@
         <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
+        <v>114</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1062,22 +1104,22 @@
         <v>46</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1088,7 +1130,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
@@ -1097,10 +1139,10 @@
         <v>19</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" t="s">
-        <v>16</v>
+        <v>91</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="H15" t="s">
         <v>12</v>
@@ -1114,22 +1156,22 @@
         <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>27</v>
+        <v>88</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
       </c>
-      <c r="H16" t="s">
-        <v>10</v>
+      <c r="H16" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1139,8 +1181,8 @@
       <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="C17" t="s">
-        <v>15</v>
+      <c r="C17" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -1165,8 +1207,8 @@
       <c r="B18" t="s">
         <v>54</v>
       </c>
-      <c r="C18" t="s">
-        <v>22</v>
+      <c r="C18" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>55</v>
@@ -1174,8 +1216,8 @@
       <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" t="s">
-        <v>12</v>
+      <c r="F18" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="G18" t="s">
         <v>16</v>
@@ -1191,8 +1233,8 @@
       <c r="B19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
-        <v>22</v>
+      <c r="C19" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
@@ -1218,22 +1260,22 @@
         <v>61</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1259,7 +1301,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1273,7 +1315,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -1282,10 +1324,10 @@
         <v>10</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1348,7 +1390,7 @@
         <v>72</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
         <v>59</v>
@@ -1377,7 +1419,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -1389,7 +1431,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1406,10 +1448,10 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
         <v>19</v>
@@ -1432,7 +1474,7 @@
         <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -1446,65 +1488,65 @@
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -1519,56 +1561,56 @@
         <v>27</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
         <v>81</v>
       </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
       <c r="C32" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
         <v>10</v>
@@ -1576,19 +1618,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
         <v>84</v>
       </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
       <c r="C34" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
